--- a/fermatrica_rep/res/dict/vis_dict.xlsx
+++ b/fermatrica_rep/res/dict/vis_dict.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F58FE88-E107-4D75-9836-E65B71913252}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C78B4D54-A573-4974-A7B6-1FFE85931431}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="768" uniqueCount="543">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="768" uniqueCount="541">
   <si>
     <t>variable</t>
   </si>
@@ -1612,12 +1612,6 @@
     <t>posm</t>
   </si>
   <si>
-    <t>Promotion</t>
-  </si>
-  <si>
-    <t>Промоушн</t>
-  </si>
-  <si>
     <t>pr</t>
   </si>
   <si>
@@ -1636,9 +1630,6 @@
     <t>Tailor Made</t>
   </si>
   <si>
-    <t>На заказ</t>
-  </si>
-  <si>
     <t>PR</t>
   </si>
   <si>
@@ -1649,6 +1640,9 @@
   </si>
   <si>
     <t>Gift Packs</t>
+  </si>
+  <si>
+    <t>POSM</t>
   </si>
 </sst>
 </file>
@@ -2879,7 +2873,7 @@
         <v>526</v>
       </c>
       <c r="D64" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
@@ -2890,7 +2884,7 @@
         <v>527</v>
       </c>
       <c r="C65" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="D65" t="s">
         <v>528</v>
@@ -2904,10 +2898,10 @@
         <v>529</v>
       </c>
       <c r="C66" t="s">
-        <v>530</v>
+        <v>540</v>
       </c>
       <c r="D66" t="s">
-        <v>531</v>
+        <v>540</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
@@ -2915,13 +2909,13 @@
         <v>43</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="C67" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="D67" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
@@ -2929,13 +2923,13 @@
         <v>43</v>
       </c>
       <c r="B68" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="C68" t="s">
+        <v>532</v>
+      </c>
+      <c r="D68" t="s">
         <v>533</v>
-      </c>
-      <c r="C68" t="s">
-        <v>534</v>
-      </c>
-      <c r="D68" t="s">
-        <v>535</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
@@ -2943,13 +2937,13 @@
         <v>43</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="C69" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="D69" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">

--- a/fermatrica_rep/res/dict/vis_dict.xlsx
+++ b/fermatrica_rep/res/dict/vis_dict.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C78B4D54-A573-4974-A7B6-1FFE85931431}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED996F1B-7330-4F33-8D88-FA2D96EDA310}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="768" uniqueCount="541">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="776" uniqueCount="547">
   <si>
     <t>variable</t>
   </si>
@@ -493,9 +493,6 @@
     <t>Инкр. продажи, руб.</t>
   </si>
   <si>
-    <t>Прибыль, руб.</t>
-  </si>
-  <si>
     <t>Прирост к *** г. по упак.</t>
   </si>
   <si>
@@ -604,9 +601,6 @@
     <t>Инвестиции</t>
   </si>
   <si>
-    <t>Прибыль</t>
-  </si>
-  <si>
     <t>axis_x</t>
   </si>
   <si>
@@ -655,9 +649,6 @@
     <t>Инкр. продажи в руб., ***</t>
   </si>
   <si>
-    <t>Прибыль, руб., ***</t>
-  </si>
-  <si>
     <t>Volume Sales ***, packs</t>
   </si>
   <si>
@@ -1189,12 +1180,6 @@
     <t>Avg. Profit ***, RUB</t>
   </si>
   <si>
-    <t>Среднегодовая прибыль, руб., *** г.</t>
-  </si>
-  <si>
-    <t>Прибыль, руб., *** г.</t>
-  </si>
-  <si>
     <t>Nat TV Halo</t>
   </si>
   <si>
@@ -1643,6 +1628,39 @@
   </si>
   <si>
     <t>POSM</t>
+  </si>
+  <si>
+    <t>profit_cum_axis_y</t>
+  </si>
+  <si>
+    <t>*** Sum. Incr. Sales, Mln. RUB</t>
+  </si>
+  <si>
+    <t>Sum. Profit ***, RUB</t>
+  </si>
+  <si>
+    <t>Суммарные инкр. продажи, млн.руб., *** г.</t>
+  </si>
+  <si>
+    <t>incr_sales_cum_axis_y</t>
+  </si>
+  <si>
+    <t>Окупаемость, руб.</t>
+  </si>
+  <si>
+    <t>Окупаемость</t>
+  </si>
+  <si>
+    <t>Окупаемость, руб., ***</t>
+  </si>
+  <si>
+    <t>Окупаемость, руб., *** г.</t>
+  </si>
+  <si>
+    <t>Среднегодовая окупаемость, руб., *** г.</t>
+  </si>
+  <si>
+    <t>Суммарная окупаемость, руб., *** г.</t>
   </si>
 </sst>
 </file>
@@ -1971,7 +1989,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D192"/>
+  <dimension ref="A1:D194"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.140625" customWidth="1"/>
@@ -1982,7 +2000,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -2170,7 +2188,7 @@
         <v>102</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="D14" t="s">
         <v>103</v>
@@ -2184,7 +2202,7 @@
         <v>29</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="D15" t="s">
         <v>34</v>
@@ -2237,13 +2255,13 @@
         <v>22</v>
       </c>
       <c r="B19" t="s">
+        <v>172</v>
+      </c>
+      <c r="C19" t="s">
         <v>173</v>
       </c>
-      <c r="C19" t="s">
+      <c r="D19" t="s">
         <v>174</v>
-      </c>
-      <c r="D19" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -2251,13 +2269,13 @@
         <v>22</v>
       </c>
       <c r="B20" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="C20" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="D20" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -2265,13 +2283,13 @@
         <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="C21" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="D21" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -2279,13 +2297,13 @@
         <v>22</v>
       </c>
       <c r="B22" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="C22" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
       <c r="D22" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -2321,7 +2339,7 @@
         <v>43</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="C25" t="s">
         <v>48</v>
@@ -2335,13 +2353,13 @@
         <v>43</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="C26" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="D26" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -2349,7 +2367,7 @@
         <v>43</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="C27" t="s">
         <v>49</v>
@@ -2363,7 +2381,7 @@
         <v>43</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="C28" t="s">
         <v>50</v>
@@ -2377,13 +2395,13 @@
         <v>43</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="C29" t="s">
+        <v>377</v>
+      </c>
+      <c r="D29" t="s">
         <v>380</v>
-      </c>
-      <c r="D29" t="s">
-        <v>383</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -2391,13 +2409,13 @@
         <v>43</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="C30" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="D30" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -2405,13 +2423,13 @@
         <v>43</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="C31" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="D31" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -2419,13 +2437,13 @@
         <v>43</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="C32" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="D32" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -2433,13 +2451,13 @@
         <v>43</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="C33" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="D33" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -2475,7 +2493,7 @@
         <v>43</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="C36" t="s">
         <v>53</v>
@@ -2489,13 +2507,13 @@
         <v>43</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="C37" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="D37" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -2503,7 +2521,7 @@
         <v>43</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="C38" t="s">
         <v>51</v>
@@ -2517,7 +2535,7 @@
         <v>43</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="C39" t="s">
         <v>52</v>
@@ -2531,7 +2549,7 @@
         <v>43</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="C40" t="s">
         <v>117</v>
@@ -2545,7 +2563,7 @@
         <v>43</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="C41" t="s">
         <v>119</v>
@@ -2559,13 +2577,13 @@
         <v>43</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="C42" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="D42" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -2573,10 +2591,10 @@
         <v>43</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="C43" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="D43" t="s">
         <v>65</v>
@@ -2587,13 +2605,13 @@
         <v>43</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="C44" t="s">
+        <v>366</v>
+      </c>
+      <c r="D44" t="s">
         <v>369</v>
-      </c>
-      <c r="D44" t="s">
-        <v>372</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -2601,13 +2619,13 @@
         <v>43</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="C45" t="s">
+        <v>367</v>
+      </c>
+      <c r="D45" t="s">
         <v>370</v>
-      </c>
-      <c r="D45" t="s">
-        <v>373</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -2615,13 +2633,13 @@
         <v>43</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="C46" t="s">
+        <v>368</v>
+      </c>
+      <c r="D46" t="s">
         <v>371</v>
-      </c>
-      <c r="D46" t="s">
-        <v>374</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -2685,7 +2703,7 @@
         <v>43</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="C51" t="s">
         <v>122</v>
@@ -2713,13 +2731,13 @@
         <v>43</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="C53" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="D53" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -2741,13 +2759,13 @@
         <v>43</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="C55" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="D55" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
@@ -2755,13 +2773,13 @@
         <v>43</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="C56" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="D56" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
@@ -2769,13 +2787,13 @@
         <v>43</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="C57" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="D57" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
@@ -2783,13 +2801,13 @@
         <v>43</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="C58" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="D58" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
@@ -2797,13 +2815,13 @@
         <v>43</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="C59" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="D59" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
@@ -2811,13 +2829,13 @@
         <v>43</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="C60" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="D60" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
@@ -2825,13 +2843,13 @@
         <v>43</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="C61" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="D61" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
@@ -2839,13 +2857,13 @@
         <v>43</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="C62" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="D62" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
@@ -2853,13 +2871,13 @@
         <v>43</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>522</v>
+        <v>517</v>
       </c>
       <c r="C63" t="s">
-        <v>523</v>
+        <v>518</v>
       </c>
       <c r="D63" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
@@ -2867,13 +2885,13 @@
         <v>43</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>525</v>
+        <v>520</v>
       </c>
       <c r="C64" t="s">
-        <v>526</v>
+        <v>521</v>
       </c>
       <c r="D64" t="s">
-        <v>538</v>
+        <v>533</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
@@ -2881,13 +2899,13 @@
         <v>43</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>527</v>
+        <v>522</v>
       </c>
       <c r="C65" t="s">
-        <v>539</v>
+        <v>534</v>
       </c>
       <c r="D65" t="s">
-        <v>528</v>
+        <v>523</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
@@ -2895,13 +2913,13 @@
         <v>43</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="C66" t="s">
-        <v>540</v>
+        <v>535</v>
       </c>
       <c r="D66" t="s">
-        <v>540</v>
+        <v>535</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
@@ -2909,13 +2927,13 @@
         <v>43</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="C67" t="s">
-        <v>536</v>
+        <v>531</v>
       </c>
       <c r="D67" t="s">
-        <v>537</v>
+        <v>532</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
@@ -2923,13 +2941,13 @@
         <v>43</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>531</v>
+        <v>526</v>
       </c>
       <c r="C68" t="s">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="D68" t="s">
-        <v>533</v>
+        <v>528</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
@@ -2937,13 +2955,13 @@
         <v>43</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>534</v>
+        <v>529</v>
       </c>
       <c r="C69" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="D69" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
@@ -2954,7 +2972,7 @@
         <v>75</v>
       </c>
       <c r="C70" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="D70" t="s">
         <v>83</v>
@@ -2976,7 +2994,7 @@
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="B72" t="s">
         <v>21</v>
@@ -3080,10 +3098,10 @@
         <v>21</v>
       </c>
       <c r="C79" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="D79" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
@@ -3108,10 +3126,10 @@
         <v>21</v>
       </c>
       <c r="C81" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="D81" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
@@ -3147,7 +3165,7 @@
         <v>105</v>
       </c>
       <c r="B84" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="C84" t="s">
         <v>115</v>
@@ -3217,13 +3235,13 @@
         <v>134</v>
       </c>
       <c r="B89" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="C89" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="D89" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
@@ -3242,86 +3260,86 @@
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B91" t="s">
         <v>21</v>
       </c>
       <c r="C91" t="s">
+        <v>162</v>
+      </c>
+      <c r="D91" t="s">
         <v>163</v>
-      </c>
-      <c r="D91" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B92" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="C92" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="D92" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B93" t="s">
         <v>21</v>
       </c>
       <c r="C93" t="s">
+        <v>165</v>
+      </c>
+      <c r="D93" t="s">
         <v>166</v>
-      </c>
-      <c r="D93" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="94" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B94" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B95" t="s">
         <v>21</v>
       </c>
       <c r="C95" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D95" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
     </row>
     <row r="96" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B96" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
@@ -3332,7 +3350,7 @@
         <v>21</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="D97" t="s">
         <v>142</v>
@@ -3382,10 +3400,10 @@
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B101" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C101" t="s">
         <v>59</v>
@@ -3396,10 +3414,10 @@
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B102" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="C102" t="s">
         <v>58</v>
@@ -3410,13 +3428,13 @@
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B103" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="C103" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D103" t="s">
         <v>156</v>
@@ -3424,38 +3442,38 @@
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B104" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="C104" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="D104" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
+        <v>158</v>
+      </c>
+      <c r="B105" t="s">
+        <v>183</v>
+      </c>
+      <c r="C105" t="s">
         <v>159</v>
       </c>
-      <c r="B105" t="s">
-        <v>184</v>
-      </c>
-      <c r="C105" t="s">
-        <v>160</v>
-      </c>
       <c r="D105" t="s">
-        <v>157</v>
+        <v>541</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B106" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="C106" t="s">
         <v>155</v>
@@ -3466,1206 +3484,1234 @@
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B107" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="C107" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D107" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B108" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="C108" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="D108" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B109" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="C109" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="D109" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B110" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="C110" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="D110" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B111" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="C111" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="D111" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
+        <v>167</v>
+      </c>
+      <c r="B112" t="s">
+        <v>170</v>
+      </c>
+      <c r="C112" t="s">
         <v>168</v>
       </c>
-      <c r="B112" t="s">
-        <v>171</v>
-      </c>
-      <c r="C112" t="s">
-        <v>169</v>
-      </c>
       <c r="D112" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B113" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C113" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D113" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
+        <v>176</v>
+      </c>
+      <c r="B114" t="s">
         <v>177</v>
       </c>
-      <c r="B114" t="s">
-        <v>178</v>
-      </c>
       <c r="C114" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="D114" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B115" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="C115" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="D115" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B116" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="C116" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="D116" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B117" t="s">
+        <v>178</v>
+      </c>
+      <c r="C117" t="s">
         <v>179</v>
       </c>
-      <c r="C117" t="s">
+      <c r="D117" t="s">
         <v>180</v>
-      </c>
-      <c r="D117" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
+        <v>186</v>
+      </c>
+      <c r="B118" t="s">
+        <v>184</v>
+      </c>
+      <c r="C118" t="s">
         <v>187</v>
       </c>
-      <c r="B118" t="s">
-        <v>185</v>
-      </c>
-      <c r="C118" t="s">
-        <v>188</v>
-      </c>
       <c r="D118" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B119" t="s">
+        <v>189</v>
+      </c>
+      <c r="C119" t="s">
         <v>190</v>
       </c>
-      <c r="C119" t="s">
-        <v>191</v>
-      </c>
       <c r="D119" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B120" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C120" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D120" t="s">
-        <v>194</v>
+        <v>542</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B121" t="s">
         <v>21</v>
       </c>
       <c r="C121" t="s">
+        <v>196</v>
+      </c>
+      <c r="D121" t="s">
         <v>198</v>
-      </c>
-      <c r="D121" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B122" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C122" t="s">
+        <v>197</v>
+      </c>
+      <c r="D122" t="s">
         <v>199</v>
-      </c>
-      <c r="D122" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B123" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C123" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D123" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B124" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C124" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="D124" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B125" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="C125" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="D125" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B126" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="C126" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="D126" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B127" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C127" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="D127" t="s">
-        <v>211</v>
+        <v>543</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
+        <v>201</v>
+      </c>
+      <c r="B128" t="s">
         <v>203</v>
       </c>
-      <c r="B128" t="s">
+      <c r="C128" t="s">
+        <v>204</v>
+      </c>
+      <c r="D128" t="s">
         <v>205</v>
-      </c>
-      <c r="C128" t="s">
-        <v>206</v>
-      </c>
-      <c r="D128" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="B129" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C129" t="s">
+        <v>197</v>
+      </c>
+      <c r="D129" t="s">
         <v>199</v>
-      </c>
-      <c r="D129" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
+        <v>213</v>
+      </c>
+      <c r="B130" t="s">
+        <v>214</v>
+      </c>
+      <c r="C130" t="s">
+        <v>215</v>
+      </c>
+      <c r="D130" t="s">
         <v>216</v>
-      </c>
-      <c r="B130" t="s">
-        <v>217</v>
-      </c>
-      <c r="C130" t="s">
-        <v>218</v>
-      </c>
-      <c r="D130" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="B131" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C131" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="D131" t="s">
-        <v>390</v>
+        <v>544</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="B132" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="C132" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="D132" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B133" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C133" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="D133" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B134" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="C134" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="D134" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B135" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="C135" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="D135" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B136" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="C136" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="D136" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B137" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C137" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="D137" t="s">
-        <v>389</v>
+        <v>545</v>
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B138" t="s">
-        <v>323</v>
+        <v>540</v>
       </c>
       <c r="C138" t="s">
-        <v>324</v>
+        <v>537</v>
       </c>
       <c r="D138" t="s">
-        <v>325</v>
+        <v>539</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="B139" t="s">
-        <v>464</v>
+        <v>536</v>
       </c>
       <c r="C139" t="s">
-        <v>472</v>
+        <v>538</v>
       </c>
       <c r="D139" t="s">
-        <v>465</v>
+        <v>546</v>
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="B140" t="s">
-        <v>466</v>
+        <v>320</v>
       </c>
       <c r="C140" t="s">
-        <v>487</v>
+        <v>321</v>
       </c>
       <c r="D140" t="s">
-        <v>486</v>
+        <v>322</v>
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B141" t="s">
-        <v>426</v>
+        <v>459</v>
       </c>
       <c r="C141" t="s">
-        <v>223</v>
+        <v>467</v>
       </c>
       <c r="D141" t="s">
-        <v>224</v>
+        <v>460</v>
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B142" t="s">
-        <v>234</v>
+        <v>461</v>
       </c>
       <c r="C142" t="s">
-        <v>225</v>
+        <v>482</v>
       </c>
       <c r="D142" t="s">
-        <v>226</v>
+        <v>481</v>
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B143" t="s">
-        <v>235</v>
+        <v>421</v>
       </c>
       <c r="C143" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="D143" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
+        <v>219</v>
+      </c>
+      <c r="B144" t="s">
+        <v>231</v>
+      </c>
+      <c r="C144" t="s">
         <v>222</v>
       </c>
-      <c r="B144" t="s">
-        <v>427</v>
-      </c>
-      <c r="C144" t="s">
-        <v>259</v>
-      </c>
       <c r="D144" t="s">
-        <v>261</v>
+        <v>223</v>
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B145" t="s">
-        <v>428</v>
+        <v>232</v>
       </c>
       <c r="C145" t="s">
-        <v>263</v>
+        <v>224</v>
       </c>
       <c r="D145" t="s">
-        <v>264</v>
+        <v>224</v>
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B146" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="C146" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="D146" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B147" t="s">
-        <v>430</v>
+        <v>423</v>
       </c>
       <c r="C147" t="s">
-        <v>230</v>
+        <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>231</v>
+        <v>261</v>
       </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B148" t="s">
-        <v>431</v>
+        <v>424</v>
       </c>
       <c r="C148" t="s">
-        <v>238</v>
+        <v>257</v>
       </c>
       <c r="D148" t="s">
-        <v>239</v>
+        <v>259</v>
       </c>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B149" t="s">
-        <v>237</v>
+        <v>425</v>
       </c>
       <c r="C149" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="D149" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B150" t="s">
-        <v>359</v>
+        <v>426</v>
       </c>
       <c r="C150" t="s">
-        <v>360</v>
+        <v>235</v>
       </c>
       <c r="D150" t="s">
-        <v>361</v>
+        <v>236</v>
       </c>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B151" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="C151" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="D151" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B152" t="s">
-        <v>243</v>
+        <v>356</v>
       </c>
       <c r="C152" t="s">
-        <v>244</v>
+        <v>357</v>
       </c>
       <c r="D152" t="s">
-        <v>245</v>
+        <v>358</v>
       </c>
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B153" t="s">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="C153" t="s">
-        <v>247</v>
+        <v>238</v>
       </c>
       <c r="D153" t="s">
-        <v>248</v>
+        <v>239</v>
       </c>
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B154" t="s">
-        <v>432</v>
+        <v>240</v>
       </c>
       <c r="C154" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="D154" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B155" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="C155" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="D155" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B156" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="C156" t="s">
-        <v>265</v>
+        <v>246</v>
       </c>
       <c r="D156" t="s">
-        <v>266</v>
+        <v>247</v>
       </c>
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B157" t="s">
-        <v>434</v>
+        <v>248</v>
       </c>
       <c r="C157" t="s">
-        <v>270</v>
+        <v>249</v>
       </c>
       <c r="D157" t="s">
-        <v>271</v>
+        <v>250</v>
       </c>
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B158" t="s">
-        <v>272</v>
+        <v>428</v>
       </c>
       <c r="C158" t="s">
-        <v>273</v>
+        <v>262</v>
       </c>
       <c r="D158" t="s">
-        <v>274</v>
+        <v>263</v>
       </c>
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B159" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="C159" t="s">
-        <v>301</v>
+        <v>267</v>
       </c>
       <c r="D159" t="s">
-        <v>302</v>
+        <v>268</v>
       </c>
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B160" t="s">
-        <v>296</v>
+        <v>269</v>
       </c>
       <c r="C160" t="s">
-        <v>297</v>
+        <v>270</v>
       </c>
       <c r="D160" t="s">
-        <v>298</v>
+        <v>271</v>
       </c>
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B161" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="C161" t="s">
-        <v>276</v>
+        <v>298</v>
       </c>
       <c r="D161" t="s">
-        <v>275</v>
+        <v>299</v>
       </c>
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B162" t="s">
-        <v>437</v>
+        <v>293</v>
       </c>
       <c r="C162" t="s">
-        <v>277</v>
+        <v>294</v>
       </c>
       <c r="D162" t="s">
-        <v>278</v>
+        <v>295</v>
       </c>
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B163" t="s">
-        <v>279</v>
+        <v>431</v>
       </c>
       <c r="C163" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="D163" t="s">
-        <v>282</v>
+        <v>272</v>
       </c>
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B164" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="C164" t="s">
-        <v>303</v>
+        <v>274</v>
       </c>
       <c r="D164" t="s">
-        <v>304</v>
+        <v>275</v>
       </c>
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B165" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="C165" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="D165" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B166" t="s">
-        <v>289</v>
+        <v>433</v>
       </c>
       <c r="C166" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="D166" t="s">
-        <v>290</v>
+        <v>301</v>
       </c>
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B167" t="s">
-        <v>439</v>
+        <v>277</v>
       </c>
       <c r="C167" t="s">
-        <v>292</v>
+        <v>280</v>
       </c>
       <c r="D167" t="s">
-        <v>293</v>
+        <v>281</v>
       </c>
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B168" t="s">
-        <v>440</v>
+        <v>286</v>
       </c>
       <c r="C168" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="D168" t="s">
-        <v>295</v>
+        <v>287</v>
       </c>
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B169" t="s">
-        <v>305</v>
+        <v>434</v>
       </c>
       <c r="C169" t="s">
-        <v>306</v>
+        <v>289</v>
       </c>
       <c r="D169" t="s">
-        <v>307</v>
+        <v>290</v>
       </c>
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B170" t="s">
-        <v>441</v>
+        <v>435</v>
       </c>
       <c r="C170" t="s">
-        <v>310</v>
+        <v>291</v>
       </c>
       <c r="D170" t="s">
-        <v>309</v>
+        <v>292</v>
       </c>
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B171" t="s">
-        <v>314</v>
+        <v>302</v>
       </c>
       <c r="C171" t="s">
-        <v>315</v>
+        <v>303</v>
       </c>
       <c r="D171" t="s">
-        <v>316</v>
+        <v>304</v>
       </c>
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B172" t="s">
-        <v>317</v>
+        <v>436</v>
       </c>
       <c r="C172" t="s">
-        <v>318</v>
+        <v>307</v>
       </c>
       <c r="D172" t="s">
-        <v>319</v>
+        <v>306</v>
       </c>
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B173" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="C173" t="s">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="D173" t="s">
-        <v>322</v>
+        <v>313</v>
       </c>
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B174" t="s">
-        <v>442</v>
+        <v>314</v>
       </c>
       <c r="C174" t="s">
-        <v>326</v>
+        <v>315</v>
       </c>
       <c r="D174" t="s">
-        <v>330</v>
+        <v>316</v>
       </c>
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B175" t="s">
-        <v>443</v>
+        <v>317</v>
       </c>
       <c r="C175" t="s">
-        <v>327</v>
+        <v>318</v>
       </c>
       <c r="D175" t="s">
-        <v>331</v>
+        <v>319</v>
       </c>
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B176" t="s">
-        <v>444</v>
+        <v>437</v>
       </c>
       <c r="C176" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="D176" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B177" t="s">
-        <v>445</v>
+        <v>438</v>
       </c>
       <c r="C177" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="D177" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B178" t="s">
-        <v>344</v>
+        <v>439</v>
       </c>
       <c r="C178" t="s">
-        <v>345</v>
+        <v>325</v>
       </c>
       <c r="D178" t="s">
-        <v>346</v>
+        <v>329</v>
       </c>
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B179" t="s">
-        <v>356</v>
+        <v>440</v>
       </c>
       <c r="C179" t="s">
-        <v>357</v>
+        <v>326</v>
       </c>
       <c r="D179" t="s">
-        <v>358</v>
+        <v>330</v>
       </c>
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B180" t="s">
-        <v>362</v>
+        <v>341</v>
       </c>
       <c r="C180" t="s">
-        <v>363</v>
+        <v>342</v>
       </c>
       <c r="D180" t="s">
-        <v>364</v>
+        <v>343</v>
       </c>
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B181" t="s">
-        <v>365</v>
+        <v>353</v>
       </c>
       <c r="C181" t="s">
-        <v>366</v>
+        <v>354</v>
       </c>
       <c r="D181" t="s">
-        <v>367</v>
+        <v>355</v>
       </c>
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B182" t="s">
-        <v>375</v>
+        <v>359</v>
       </c>
       <c r="C182" t="s">
-        <v>376</v>
+        <v>360</v>
       </c>
       <c r="D182" t="s">
-        <v>377</v>
+        <v>361</v>
       </c>
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B183" t="s">
-        <v>446</v>
+        <v>362</v>
       </c>
       <c r="C183" t="s">
-        <v>393</v>
+        <v>363</v>
       </c>
       <c r="D183" t="s">
-        <v>394</v>
+        <v>364</v>
       </c>
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B184" t="s">
-        <v>450</v>
+        <v>372</v>
       </c>
       <c r="C184" t="s">
-        <v>449</v>
+        <v>373</v>
       </c>
       <c r="D184" t="s">
-        <v>448</v>
+        <v>374</v>
       </c>
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B185" t="s">
-        <v>454</v>
+        <v>441</v>
       </c>
       <c r="C185" t="s">
-        <v>455</v>
+        <v>388</v>
       </c>
       <c r="D185" t="s">
-        <v>456</v>
+        <v>389</v>
       </c>
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>490</v>
+        <v>219</v>
       </c>
       <c r="B186" t="s">
-        <v>491</v>
+        <v>445</v>
       </c>
       <c r="C186" t="s">
-        <v>493</v>
+        <v>444</v>
       </c>
       <c r="D186" t="s">
-        <v>494</v>
+        <v>443</v>
       </c>
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>490</v>
+        <v>219</v>
       </c>
       <c r="B187" t="s">
-        <v>492</v>
+        <v>449</v>
       </c>
       <c r="C187" t="s">
-        <v>493</v>
+        <v>450</v>
       </c>
       <c r="D187" t="s">
-        <v>495</v>
+        <v>451</v>
       </c>
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="B188" t="s">
-        <v>195</v>
+        <v>486</v>
       </c>
       <c r="C188" t="s">
-        <v>505</v>
+        <v>488</v>
       </c>
       <c r="D188" t="s">
-        <v>496</v>
+        <v>489</v>
       </c>
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
+        <v>485</v>
+      </c>
+      <c r="B189" t="s">
+        <v>487</v>
+      </c>
+      <c r="C189" t="s">
+        <v>488</v>
+      </c>
+      <c r="D189" t="s">
         <v>490</v>
-      </c>
-      <c r="B189" t="s">
-        <v>497</v>
-      </c>
-      <c r="C189" t="s">
-        <v>500</v>
-      </c>
-      <c r="D189" t="s">
-        <v>502</v>
       </c>
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="B190" t="s">
-        <v>106</v>
+        <v>193</v>
       </c>
       <c r="C190" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="D190" t="s">
-        <v>504</v>
+        <v>491</v>
       </c>
     </row>
     <row r="191" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="B191" t="s">
-        <v>498</v>
+        <v>492</v>
       </c>
       <c r="C191" t="s">
-        <v>501</v>
+        <v>495</v>
       </c>
       <c r="D191" t="s">
-        <v>503</v>
+        <v>497</v>
       </c>
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="B192" t="s">
-        <v>196</v>
+        <v>106</v>
       </c>
       <c r="C192" t="s">
-        <v>506</v>
+        <v>494</v>
       </c>
       <c r="D192" t="s">
-        <v>507</v>
+        <v>499</v>
+      </c>
+    </row>
+    <row r="193" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>485</v>
+      </c>
+      <c r="B193" t="s">
+        <v>493</v>
+      </c>
+      <c r="C193" t="s">
+        <v>496</v>
+      </c>
+      <c r="D193" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="194" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
+        <v>485</v>
+      </c>
+      <c r="B194" t="s">
+        <v>194</v>
+      </c>
+      <c r="C194" t="s">
+        <v>501</v>
+      </c>
+      <c r="D194" t="s">
+        <v>502</v>
       </c>
     </row>
   </sheetData>
